--- a/Excel/LevelData.xlsx
+++ b/Excel/LevelData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="30720" windowHeight="13380"/>
+    <workbookView windowWidth="22091" windowHeight="9527"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1209,7 +1209,7 @@
         <v>1.5</v>
       </c>
       <c r="L13">
-        <v>2</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="14" spans="1:12">
